--- a/apps/alarmx/economics/AlarmX-unit-economics.xlsx
+++ b/apps/alarmx/economics/AlarmX-unit-economics.xlsx
@@ -44,6 +44,12 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <sz val="10"/>
     </font>
     <font>
@@ -62,12 +68,6 @@
     </font>
     <font>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
       <i val="1"/>
       <color rgb="00595959"/>
       <sz val="9"/>
@@ -82,17 +82,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFFF00"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F3864"/>
       </patternFill>
     </fill>
     <fill>
@@ -135,83 +135,83 @@
   <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="3" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -579,7 +579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A53"/>
+  <dimension ref="A1:A92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -588,7 +588,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AlarmX — Unit Economics Model (v0.4)</t>
+          <t>AlarmX — Unit Economics Model (v0.5)</t>
         </is>
       </c>
     </row>
@@ -622,70 +622,62 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>What changed in v0.4 — deliberately, almost nothing</t>
+          <t>WHERE THE MONEY ACTUALLY COMES FROM</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>v0.4 adds the regional calendar and the 4x2 home-screen widget (PRD 16).</t>
+          <t>Advertising is the largest source and always was. Per active user per month:</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>It pays no cash, so it does not touch the cap. Two accounting notes:</t>
-        </is>
-      </c>
+      <c r="A9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Swiss Ephemeris Professional licence: a ONE-TIME CAPITALISED COST, paid</t>
+          <t xml:space="preserve">                        Conservative      Base   Optimistic</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    per project before distribution. It is not a per-user cost and must not be</t>
+          <t xml:space="preserve">  Advertising                  Rs5.62   Rs15.91      Rs43.68</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    amortised into the cap. Get the current fee from Astrodienst before booking it.</t>
+          <t xml:space="preserve">  Survey resale                Rs5.67   Rs10.25      Rs20.00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - The widget MAY raise active days per month (Base assumes 26). That would</t>
+          <t xml:space="preserve">  Ads as a share of revenue       50%       61%          69%</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    raise revenue and therefore the cap. IT IS NOT BAKED IN, AND MUST NOT BE.</t>
-        </is>
-      </c>
+      <c r="A14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Raising a revenue assumption on the strength of an unshipped feature is how</t>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>SO WHY DOES THE SURVEY PLACEHOLDER STILL MATTER? Because of this:</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    the Rs95 design happened. Re-measure after 60 days of live data, then decide.</t>
+          <t>With the survey line set to ZERO, ads alone produce these caps:</t>
         </is>
       </c>
     </row>
@@ -693,44 +685,40 @@
       <c r="A17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>What changed in v0.3</t>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Conservative   ad revenue Rs5.62  vs non-reward cost Rs5.95  -&gt;  cap NEGATIVE</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>The first payout drops from Rs30 to Rs10. That is not free:</t>
+          <t xml:space="preserve">  Base           ad revenue Rs15.91                            -&gt;  cap Rs10.08</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Fewer users churn without ever withdrawing, so BREAKAGE FALLS.</t>
+          <t xml:space="preserve">  Optimistic     ad revenue Rs43.68                            -&gt;  cap Rs47.10</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - Lower breakage means more of what is accrued is actually paid out.</t>
-        </is>
-      </c>
+      <c r="A21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Higher real cash cost means the SUSTAINABLE CAP FALLS.</t>
+          <t>In the Conservative column ad revenue does not cover the payout fee, servers</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>The Model tab quantifies exactly how much, and compares against v0.2.</t>
+          <t>and support. You lose money before paying a single reward.</t>
         </is>
       </c>
     </row>
@@ -738,191 +726,440 @@
       <c r="A24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>The first payout is booked as ACQUISITION, not as a reward.</t>
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Leaning on ads does not remove that fragility, it MOVES it. The load-bearing</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Rs10 plus the payout fee buys the 'it actually paid me' moment, which is a</t>
+          <t>input stops being a survey price you can negotiate and becomes eCPM and fill</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>marketing outcome. The same rupees spent on an install ad would buy far less.</t>
+          <t>rate, which Google sets and you do not. Both need real measurement.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>Charging it to the reward budget would wrongly depress the cap in every later</t>
-        </is>
-      </c>
+      <c r="A28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>month. It sits in its own block on the Model tab, compared against install cost.</t>
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>What changed in v0.5</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr"/>
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Rewarded video goes from 3 to 4 views per active day at Base.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>How to use it</t>
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Rewarded eCPM is $1.50 against $0.40 for interstitial, so an extra rewarded</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>1. Assumptions tab. Edit ONLY the blue cells.</t>
+          <t>view is worth 3.8x an extra interstitial - and the user opts into it.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2. Three scenarios: Conservative / Base / Optimistic. Base is the planning case.</t>
+          <t xml:space="preserve">  Base cap Rs16.75 -&gt; Rs19.19.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>3. Model computes the cap per scenario. Nothing there is typed by hand.</t>
-        </is>
-      </c>
+      <c r="A34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>4. Scale shows monthly P&amp;L at 10k / 100k / 1M MAU. Set your cap in the yellow cell.</t>
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>THE LAUNCH CAP STAYS AT Rs15. The extra headroom is banked as margin, not</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>5. Sensitivity grids cap against revenue per user.</t>
+          <t>spent. Four videos a day is an assumption, not a measurement. Raising the</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr"/>
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>payout on the strength of an unmeasured assumption is exactly the mistake</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>Colour key</t>
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>that produced the Rs95 design.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>Blue text = hardcoded input you can edit</t>
-        </is>
-      </c>
+      <c r="A39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>Black text = formula, do not overwrite</t>
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>NO AD SITS BETWEEN THE USER AND ALARM DISMISSAL. An interstitial there was</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>Green text = link to another sheet</t>
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>modelled and priced: it earns Rs0.73/user/month and moves the cap Rs0.65.</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>Yellow fill = load-bearing assumption</t>
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>That is the entire value of delaying someone switching off a 5am alarm, and</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="7" t="inlineStr">
-        <is>
-          <t>Orange fill = acquisition, deliberately outside the reward budget</t>
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>of handing a Play reviewer a reward app that blocks an alarm. Not taken.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr"/>
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>The 4 interstitials above sit in allowed slots only - see PRD 4.6.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>Sources</t>
-        </is>
-      </c>
+      <c r="A45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>Rewarded video eCPM: India Android rewarded benchmarked around $1.50; India across</t>
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>What changed in v0.4 — deliberately, almost nothing</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ad types spans $0.50-$2.00. Source: Coinis rewarded-video glossary; Business of Apps.</t>
+          <t>v0.4 adds the regional calendar and the 4x2 home-screen widget (PRD 16).</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>UPI payout fee: RazorpayX Rs2-5 per payout, UPI at the low end. Verify the live</t>
+          <t>It pays no cash, so it does not touch the cap. Two accounting notes:</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  price card before committing.</t>
+          <t xml:space="preserve">  - Swiss Ephemeris Professional licence: a ONE-TIME CAPITALISED COST, paid</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>Survey resale values: NOT SOURCED. Placeholders, and the least reliable inputs here.</t>
+          <t xml:space="preserve">    per project before distribution. It is not a per-user cost and must not be</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Validate with a real data buyer before counting this revenue.</t>
+          <t xml:space="preserve">    amortised into the cap. Get the current fee from Astrodienst before booking it.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>Breakage and share-reaching-first-payout: assumptions, not measured. Revisit after</t>
+          <t xml:space="preserve">  - The widget MAY raise active days per month (Base assumes 26). That would</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    raise revenue and therefore the cap. IT IS NOT BAKED IN, AND MUST NOT BE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Raising a revenue assumption on the strength of an unshipped feature is how</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    the Rs95 design happened. Re-measure after 60 days of live data, then decide.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>What changed in v0.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>The first payout drops from Rs30 to Rs10. That is not free:</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Fewer users churn without ever withdrawing, so BREAKAGE FALLS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Lower breakage means more of what is accrued is actually paid out.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Higher real cash cost means the SUSTAINABLE CAP FALLS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>The Model tab quantifies exactly how much, and compares against v0.2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>The first payout is booked as ACQUISITION, not as a reward.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>Rs10 plus the payout fee buys the 'it actually paid me' moment, which is a</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>marketing outcome. The same rupees spent on an install ad would buy far less.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>Charging it to the reward budget would wrongly depress the cap in every later</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>month. It sits in its own block on the Model tab, compared against install cost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>How to use it</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>1. Assumptions tab. Edit ONLY the blue cells.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>2. Three scenarios: Conservative / Base / Optimistic. Base is the planning case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>3. Model computes the cap per scenario. Nothing there is typed by hand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>4. Scale shows monthly P&amp;L at 10k / 100k / 1M MAU. Set your cap in the yellow cell.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>5. Sensitivity grids cap against revenue per user.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Colour key</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>Blue text = hardcoded input you can edit</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>Black text = formula, do not overwrite</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>Green text = link to another sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>Yellow fill = load-bearing assumption</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="7" t="inlineStr">
+        <is>
+          <t>Orange fill = acquisition, deliberately outside the reward budget</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>Rewarded video eCPM: India Android rewarded benchmarked around $1.50; India across</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ad types spans $0.50-$2.00. Source: Coinis rewarded-video glossary; Business of Apps.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>UPI payout fee: RazorpayX Rs2-5 per payout, UPI at the low end. Verify the live</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  price card before committing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>Survey resale values: NOT SOURCED. Placeholders, and the least reliable inputs here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Validate with a real data buyer before counting this revenue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>Breakage and share-reaching-first-payout: assumptions, not measured. Revisit after</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">  60 days of live data - they move the cap more than almost anything else.</t>
         </is>
@@ -1098,13 +1335,13 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D9" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
@@ -1113,7 +1350,7 @@
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>Assumption</t>
+          <t>v0.5 — raised from 2/3/4. Opt-in, and worth 3.8x an interstitial</t>
         </is>
       </c>
     </row>
@@ -1165,7 +1402,7 @@
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>Materially below rewarded video</t>
+          <t>Materially below rewarded video — 27% of it at base</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1428,7 @@
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>Assumption</t>
+          <t>Allowed slots only — NONE in the alarm dismissal path, PRD 4.6</t>
         </is>
       </c>
     </row>

--- a/apps/alarmx/economics/AlarmX-unit-economics.xlsx
+++ b/apps/alarmx/economics/AlarmX-unit-economics.xlsx
@@ -132,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -184,17 +184,17 @@
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -211,9 +211,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -579,7 +576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A92"/>
+  <dimension ref="A1:A106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -588,7 +585,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AlarmX — Unit Economics Model (v0.5)</t>
+          <t>AlarmX — Unit Economics Model (v0.6)</t>
         </is>
       </c>
     </row>
@@ -598,21 +595,21 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>What this answers</t>
+          <t>THE ONE IDEA IN THIS MODEL</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>How much cash AlarmX can pay one user per month without losing money.</t>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>The user is paid a SHARE OF AD REVENUE THAT HAS ALREADY ARRIVED.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Every other number in the product spec is derived from that one.</t>
+          <t>Not a rate. Not a cap. A share of money already in the account.</t>
         </is>
       </c>
     </row>
@@ -620,88 +617,92 @@
       <c r="A6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>WHERE THE MONEY ACTUALLY COMES FROM</t>
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Every rupee credited is backed by an ad impression the SERVER has verified.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Advertising is the largest source and always was. Per active user per month:</t>
+          <t xml:space="preserve">  no ad served      -&gt; nothing credited, nothing owed</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  eCPM halves       -&gt; payouts halve the same day, automatically</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">                        Conservative      Base   Optimistic</t>
+          <t xml:space="preserve">  fill drops        -&gt; payouts drop with it</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Advertising                  Rs5.62   Rs15.91      Rs43.68</t>
+          <t xml:space="preserve">  client claims a view the server did not see -&gt; not credited</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Survey resale                Rs5.67   Rs10.25      Rs20.00</t>
-        </is>
-      </c>
+      <c r="A12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Ads as a share of revenue       50%       61%          69%</t>
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>This makes a loss on the reward line STRUCTURALLY IMPOSSIBLE, not merely</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>unlikely. There is no forecast to be wrong about, because nothing is</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>SO WHY DOES THE SURVEY PLACEHOLDER STILL MATTER? Because of this:</t>
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>promised before the money exists.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>With the survey line set to ZERO, ads alone produce these caps:</t>
-        </is>
-      </c>
+      <c r="A16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Every earlier version failed the same way: a FIXED promise made against</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Conservative   ad revenue Rs5.62  vs non-reward cost Rs5.95  -&gt;  cap NEGATIVE</t>
+          <t>VARIABLE revenue. Rs95/month. Rs0.50 a math. Rs2 a set. Each one was a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Base           ad revenue Rs15.91                            -&gt;  cap Rs10.08</t>
+          <t>number chosen first and defended afterwards. This one cannot be wrong,</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Optimistic     ad revenue Rs43.68                            -&gt;  cap Rs47.10</t>
+          <t>because it is a fraction of whatever actually turns up.</t>
         </is>
       </c>
     </row>
@@ -709,393 +710,397 @@
       <c r="A21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>In the Conservative column ad revenue does not cover the payout fee, servers</t>
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>WHAT IT PAYS AND WHAT IT KEEPS</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>and support. You lose money before paying a single reward.</t>
+          <t xml:space="preserve">                        Conservative      Base   Optimistic</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr"/>
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Ad revenue                  Rs10.55   Rs32.38     Rs103.08</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Leaning on ads does not remove that fragility, it MOVES it. The load-bearing</t>
+          <t xml:space="preserve">  Survey resale (retained)     Rs5.67   Rs10.25      Rs20.00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>input stops being a survey price you can negotiate and becomes eCPM and fill</t>
+          <t xml:space="preserve">  User earns (60% tier)        Rs6.33   Rs19.43      Rs61.85</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>rate, which Google sets and you do not. Both need real measurement.</t>
+          <t xml:space="preserve">  Per active day               Rs0.32    Rs0.75       Rs2.06</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PROFIT                       Rs3.30   Rs19.03      Rs58.24</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>What changed in v0.5</t>
-        </is>
-      </c>
+      <c r="A29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Rewarded video goes from 3 to 4 views per active day at Base.</t>
+          <t>Profit is positive in EVERY column at the HIGHEST share tier. The Model</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Rewarded eCPM is $1.50 against $0.40 for interstitial, so an extra rewarded</t>
+          <t>tab also shows profit if eCPM halved - still positive everywhere.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>view is worth 3.8x an extra interstitial - and the user opts into it.</t>
-        </is>
-      </c>
+      <c r="A32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Base cap Rs16.75 -&gt; Rs19.19.</t>
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>THE SHARE LADDER</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr"/>
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  days 1-6      50%</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>THE LAUNCH CAP STAYS AT Rs15. The extra headroom is banked as margin, not</t>
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  day 7+        55%      streak reward that costs nothing already unearned</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>spent. Four videos a day is an assumption, not a measurement. Raising the</t>
+          <t xml:space="preserve">  day 30+       60%      the worst case, and what profit is tested against</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>payout on the strength of an unmeasured assumption is exactly the mistake</t>
+          <t xml:space="preserve">  until Rs10    70%      acquisition spend, gets the user paid fast</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>that produced the Rs95 design.</t>
-        </is>
-      </c>
+      <c r="A38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr"/>
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>THE MONTHLY CAP IS GONE. Replaced by a ceiling of 20 credited ad views a</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>NO AD SITS BETWEEN THE USER AND ALARM DISMISSAL. An interstitial there was</t>
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>day. A monthly cap made the app go dead once a user hit it - earning</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>modelled and priced: it earns Rs0.73/user/month and moves the cap Rs0.65.</t>
+          <t>nothing for the rest of the cycle, which is the opposite of retention.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>That is the entire value of delaying someone switching off a 5am alarm, and</t>
+          <t>A daily ceiling bounds fraud without ever doing that.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>of handing a Play reviewer a reward app that blocks an alarm. Not taken.</t>
-        </is>
-      </c>
+      <c r="A43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>The 4 interstitials above sit in allowed slots only - see PRD 4.6.</t>
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>THE BUILD GATE</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr"/>
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>build_model.py refuses to write this file if any scenario, at any share</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>What changed in v0.4 — deliberately, almost nothing</t>
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>tier, at half or a quarter of the assumed eCPM, would lose money.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>v0.4 adds the regional calendar and the 4x2 home-screen widget (PRD 16).</t>
+          <t>36 combinations, checked on every build. The gate has been tested by</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>It pays no cash, so it does not touch the cap. Two accounting notes:</t>
+          <t>deliberately breaking it.</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - Swiss Ephemeris Professional licence: a ONE-TIME CAPITALISED COST, paid</t>
-        </is>
-      </c>
+      <c r="A49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    per project before distribution. It is not a per-user cost and must not be</t>
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>STILL THE WEAKEST INPUTS</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    amortised into the cap. Get the current fee from Astrodienst before booking it.</t>
+          <t xml:space="preserve">  1. Average sets completed per day. The revenue case leans on it and it</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - The widget MAY raise active days per month (Base assumes 26). That would</t>
+          <t xml:space="preserve">     has never been measured. It is deliberately the assumption carrying</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    raise revenue and therefore the cap. IT IS NOT BAKED IN, AND MUST NOT BE.</t>
+          <t xml:space="preserve">     the uncertainty, rather than hiding it in a rate.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Raising a revenue assumption on the strength of an unshipped feature is how</t>
+          <t xml:space="preserve">  2. Rewarded eCPM and fill rate for India Android. Published benchmarks,</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    the Rs95 design happened. Re-measure after 60 days of live data, then decide.</t>
+          <t xml:space="preserve">     not measurements. Open a real AdMob account before trusting Base.</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr"/>
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  3. Survey resale values. Placeholders. But note: the user is paid from</t>
+        </is>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>What changed in v0.3</t>
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     AD REVENUE ONLY, so a zero survey line reduces profit, never the</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>The first payout drops from Rs30 to Rs10. That is not free:</t>
+          <t xml:space="preserve">     payout, and never below zero.</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - Fewer users churn without ever withdrawing, so BREAKAGE FALLS.</t>
-        </is>
-      </c>
+      <c r="A59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - Lower breakage means more of what is accrued is actually paid out.</t>
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>What changed in v0.4 — deliberately, almost nothing</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Higher real cash cost means the SUSTAINABLE CAP FALLS.</t>
+          <t>v0.4 adds the regional calendar and the 4x2 home-screen widget (PRD 16).</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>The Model tab quantifies exactly how much, and compares against v0.2.</t>
+          <t>It pays no cash, so it does not touch the cap. Two accounting notes:</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr"/>
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Swiss Ephemeris Professional licence: a ONE-TIME CAPITALISED COST, paid</t>
+        </is>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>The first payout is booked as ACQUISITION, not as a reward.</t>
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    per project before distribution. It is not a per-user cost and must not be</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>Rs10 plus the payout fee buys the 'it actually paid me' moment, which is a</t>
+          <t xml:space="preserve">    amortised into the cap. Get the current fee from Astrodienst before booking it.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>marketing outcome. The same rupees spent on an install ad would buy far less.</t>
+          <t xml:space="preserve">  - The widget MAY raise active days per month (Base assumes 26). That would</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>Charging it to the reward budget would wrongly depress the cap in every later</t>
+          <t xml:space="preserve">    raise revenue and therefore the cap. IT IS NOT BAKED IN, AND MUST NOT BE.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>month. It sits in its own block on the Model tab, compared against install cost.</t>
+          <t xml:space="preserve">    Raising a revenue assumption on the strength of an unshipped feature is how</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr"/>
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    the Rs95 design happened. Re-measure after 60 days of live data, then decide.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>How to use it</t>
-        </is>
-      </c>
+      <c r="A70" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="3" t="inlineStr">
-        <is>
-          <t>1. Assumptions tab. Edit ONLY the blue cells.</t>
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>What changed in v0.3</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>2. Three scenarios: Conservative / Base / Optimistic. Base is the planning case.</t>
+          <t>The first payout drops from Rs30 to Rs10. That is not free:</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>3. Model computes the cap per scenario. Nothing there is typed by hand.</t>
+          <t xml:space="preserve">  - Fewer users churn without ever withdrawing, so BREAKAGE FALLS.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>4. Scale shows monthly P&amp;L at 10k / 100k / 1M MAU. Set your cap in the yellow cell.</t>
+          <t xml:space="preserve">  - Lower breakage means more of what is accrued is actually paid out.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>5. Sensitivity grids cap against revenue per user.</t>
+          <t xml:space="preserve">  - Higher real cash cost means the SUSTAINABLE CAP FALLS.</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr"/>
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>The Model tab quantifies exactly how much, and compares against v0.2.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>Colour key</t>
-        </is>
-      </c>
+      <c r="A77" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="4" t="inlineStr">
-        <is>
-          <t>Blue text = hardcoded input you can edit</t>
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>The first payout is booked as ACQUISITION, not as a reward.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>Black text = formula, do not overwrite</t>
+          <t>Rs10 plus the payout fee buys the 'it actually paid me' moment, which is a</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="5" t="inlineStr">
-        <is>
-          <t>Green text = link to another sheet</t>
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>marketing outcome. The same rupees spent on an install ad would buy far less.</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="6" t="inlineStr">
-        <is>
-          <t>Yellow fill = load-bearing assumption</t>
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>Charging it to the reward budget would wrongly depress the cap in every later</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="7" t="inlineStr">
-        <is>
-          <t>Orange fill = acquisition, deliberately outside the reward budget</t>
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>month. It sits in its own block on the Model tab, compared against install cost.</t>
         </is>
       </c>
     </row>
@@ -1105,61 +1110,151 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Sources</t>
+          <t>How to use it</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>Rewarded video eCPM: India Android rewarded benchmarked around $1.50; India across</t>
+          <t>1. Assumptions tab. Edit ONLY the blue cells.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ad types spans $0.50-$2.00. Source: Coinis rewarded-video glossary; Business of Apps.</t>
+          <t>2. Three scenarios: Conservative / Base / Optimistic. Base is the planning case.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>UPI payout fee: RazorpayX Rs2-5 per payout, UPI at the low end. Verify the live</t>
+          <t>3. Model computes the cap per scenario. Nothing there is typed by hand.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  price card before committing.</t>
+          <t>4. Scale shows monthly P&amp;L at 10k / 100k / 1M MAU. Set your cap in the yellow cell.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
+          <t>5. Sensitivity grids cap against revenue per user.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>Colour key</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>Blue text = hardcoded input you can edit</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>Black text = formula, do not overwrite</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>Green text = link to another sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>Yellow fill = load-bearing assumption</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="7" t="inlineStr">
+        <is>
+          <t>Orange fill = acquisition, deliberately outside the reward budget</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>Rewarded video eCPM: India Android rewarded benchmarked around $1.50; India across</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ad types spans $0.50-$2.00. Source: Coinis rewarded-video glossary; Business of Apps.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>UPI payout fee: RazorpayX Rs2-5 per payout, UPI at the low end. Verify the live</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  price card before committing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
           <t>Survey resale values: NOT SOURCED. Placeholders, and the least reliable inputs here.</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="3" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">  Validate with a real data buyer before counting this revenue.</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="3" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="3" t="inlineStr">
         <is>
           <t>Breakage and share-reaching-first-payout: assumptions, not measured. Revisit after</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="3" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">  60 days of live data - they move the cap more than almost anything else.</t>
         </is>
@@ -1176,7 +1271,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2024,6 +2119,264 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>MATH SECTION — the daytime earning loop (PRD 4.7)</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="n"/>
+      <c r="C40" s="10" t="n"/>
+      <c r="D40" s="10" t="n"/>
+      <c r="E40" s="10" t="n"/>
+      <c r="F40" s="10" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>Math sets offered per day</t>
+        </is>
+      </c>
+      <c r="B41" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="C41" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D41" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E41" s="13" t="inlineStr">
+        <is>
+          <t>sets</t>
+        </is>
+      </c>
+      <c r="F41" s="14" t="inlineStr">
+        <is>
+          <t>Locked until the day's alarm is completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="11" t="inlineStr">
+        <is>
+          <t>Maths per set</t>
+        </is>
+      </c>
+      <c r="B42" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="C42" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D42" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E42" s="13" t="inlineStr">
+        <is>
+          <t>questions</t>
+        </is>
+      </c>
+      <c r="F42" s="14" t="inlineStr">
+        <is>
+          <t>20 questions a day if every set is taken</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="11" t="inlineStr">
+        <is>
+          <t>Rewarded ads per set</t>
+        </is>
+      </c>
+      <c r="B43" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C43" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D43" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E43" s="13" t="inlineStr">
+        <is>
+          <t>views</t>
+        </is>
+      </c>
+      <c r="F43" s="14" t="inlineStr">
+        <is>
+          <t>One after every 2 questions</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="11" t="inlineStr">
+        <is>
+          <t>Average sets completed per day</t>
+        </is>
+      </c>
+      <c r="B44" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C44" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D44" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E44" s="13" t="inlineStr">
+        <is>
+          <t>sets</t>
+        </is>
+      </c>
+      <c r="F44" s="14" t="inlineStr">
+        <is>
+          <t>THE honest home for the uncertainty. Measure this after launch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>REVENUE SHARE — what the user is paid (PRD 2)</t>
+        </is>
+      </c>
+      <c r="B45" s="10" t="n"/>
+      <c r="C45" s="10" t="n"/>
+      <c r="D45" s="10" t="n"/>
+      <c r="E45" s="10" t="n"/>
+      <c r="F45" s="10" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="11" t="inlineStr">
+        <is>
+          <t>User share of realised ad revenue</t>
+        </is>
+      </c>
+      <c r="B46" s="16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C46" s="16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D46" s="16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E46" s="13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F46" s="14" t="inlineStr">
+        <is>
+          <t>Paid only against ad views the SERVER has verified. No view, no credit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="11" t="inlineStr">
+        <is>
+          <t>Share at a 7-day streak</t>
+        </is>
+      </c>
+      <c r="B47" s="16" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="C47" s="16" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="D47" s="16" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E47" s="13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F47" s="14" t="inlineStr">
+        <is>
+          <t>Retention lever. Costs nothing that was not already earned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="11" t="inlineStr">
+        <is>
+          <t>Share at a 30-day streak</t>
+        </is>
+      </c>
+      <c r="B48" s="16" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C48" s="16" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D48" s="16" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E48" s="13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F48" s="14" t="inlineStr">
+        <is>
+          <t>WORST CASE for the business — profit is tested against this</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="11" t="inlineStr">
+        <is>
+          <t>Share until lifetime earnings reach the first threshold</t>
+        </is>
+      </c>
+      <c r="B49" s="16" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C49" s="16" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D49" s="16" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E49" s="13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F49" s="14" t="inlineStr">
+        <is>
+          <t>Acquisition spend, gets the user to their first real payout fast</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="11" t="inlineStr">
+        <is>
+          <t>Daily credited ad views ceiling</t>
+        </is>
+      </c>
+      <c r="B50" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C50" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="D50" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="E50" s="13" t="inlineStr">
+        <is>
+          <t>views</t>
+        </is>
+      </c>
+      <c r="F50" s="14" t="inlineStr">
+        <is>
+          <t>Replaces the monthly cap. Bounds fraud without the app going dead mid-month.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2035,7 +2388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -2100,7 +2453,7 @@
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>Rewarded video</t>
+          <t>Rewarded video — standing offer</t>
         </is>
       </c>
       <c r="B6" s="25">
@@ -2124,59 +2477,67 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>Interstitial</t>
+          <t>Rewarded video — math section</t>
         </is>
       </c>
       <c r="B7" s="25">
-        <f>Assumptions!B11*Assumptions!B5/1000*Assumptions!B12*Assumptions!B6*Assumptions!B10</f>
+        <f>Assumptions!B8*Assumptions!B5/1000*MIN(Assumptions!B44*Assumptions!B43,MAX(0,Assumptions!B50-Assumptions!B9))*Assumptions!B6*Assumptions!B10</f>
         <v/>
       </c>
       <c r="C7" s="25">
-        <f>Assumptions!C11*Assumptions!C5/1000*Assumptions!C12*Assumptions!C6*Assumptions!C10</f>
+        <f>Assumptions!C8*Assumptions!C5/1000*MIN(Assumptions!C44*Assumptions!C43,MAX(0,Assumptions!C50-Assumptions!C9))*Assumptions!C6*Assumptions!C10</f>
         <v/>
       </c>
       <c r="D7" s="25">
-        <f>Assumptions!D11*Assumptions!D5/1000*Assumptions!D12*Assumptions!D6*Assumptions!D10</f>
-        <v/>
-      </c>
-      <c r="E7" s="14" t="inlineStr"/>
+        <f>Assumptions!D8*Assumptions!D5/1000*MIN(Assumptions!D44*Assumptions!D43,MAX(0,Assumptions!D50-Assumptions!D9))*Assumptions!D6*Assumptions!D10</f>
+        <v/>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>Sets completed × ads per set, inside the daily ceiling</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>Banner</t>
+          <t>Interstitial</t>
         </is>
       </c>
       <c r="B8" s="25">
-        <f>Assumptions!B13</f>
+        <f>Assumptions!B11*Assumptions!B5/1000*Assumptions!B12*Assumptions!B6*Assumptions!B10</f>
         <v/>
       </c>
       <c r="C8" s="25">
-        <f>Assumptions!C13</f>
+        <f>Assumptions!C11*Assumptions!C5/1000*Assumptions!C12*Assumptions!C6*Assumptions!C10</f>
         <v/>
       </c>
       <c r="D8" s="25">
-        <f>Assumptions!D13</f>
-        <v/>
-      </c>
-      <c r="E8" s="14" t="inlineStr"/>
+        <f>Assumptions!D11*Assumptions!D5/1000*Assumptions!D12*Assumptions!D6*Assumptions!D10</f>
+        <v/>
+      </c>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>Allowed slots only — never in the alarm dismissal path</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>Survey — one-time profile, amortised</t>
+          <t>Banner</t>
         </is>
       </c>
       <c r="B9" s="25">
-        <f>Assumptions!B15/Assumptions!B16</f>
+        <f>Assumptions!B13</f>
         <v/>
       </c>
       <c r="C9" s="25">
-        <f>Assumptions!C15/Assumptions!C16</f>
+        <f>Assumptions!C13</f>
         <v/>
       </c>
       <c r="D9" s="25">
-        <f>Assumptions!D15/Assumptions!D16</f>
+        <f>Assumptions!D13</f>
         <v/>
       </c>
       <c r="E9" s="14" t="inlineStr"/>
@@ -2184,551 +2545,588 @@
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>Survey — daily drip</t>
+          <t>Survey — one-time profile, amortised</t>
         </is>
       </c>
       <c r="B10" s="25">
-        <f>Assumptions!B17*Assumptions!B6</f>
+        <f>Assumptions!B15/Assumptions!B16</f>
         <v/>
       </c>
       <c r="C10" s="25">
-        <f>Assumptions!C17*Assumptions!C6</f>
+        <f>Assumptions!C15/Assumptions!C16</f>
         <v/>
       </c>
       <c r="D10" s="25">
-        <f>Assumptions!D17*Assumptions!D6</f>
-        <v/>
-      </c>
-      <c r="E10" s="14" t="inlineStr">
-        <is>
-          <t>Why the survey drips instead of dumping once</t>
-        </is>
-      </c>
+        <f>Assumptions!D15/Assumptions!D16</f>
+        <v/>
+      </c>
+      <c r="E10" s="14" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
+          <t>Survey — daily drip</t>
+        </is>
+      </c>
+      <c r="B11" s="25">
+        <f>Assumptions!B17*Assumptions!B6</f>
+        <v/>
+      </c>
+      <c r="C11" s="25">
+        <f>Assumptions!C17*Assumptions!C6</f>
+        <v/>
+      </c>
+      <c r="D11" s="25">
+        <f>Assumptions!D17*Assumptions!D6</f>
+        <v/>
+      </c>
+      <c r="E11" s="14" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
           <t>Sponsored QR (dormant)</t>
         </is>
       </c>
-      <c r="B11" s="25">
+      <c r="B12" s="25">
         <f>Assumptions!B19*Assumptions!B20*Assumptions!B6</f>
         <v/>
       </c>
-      <c r="C11" s="25">
+      <c r="C12" s="25">
         <f>Assumptions!C19*Assumptions!C20*Assumptions!C6</f>
         <v/>
       </c>
-      <c r="D11" s="25">
+      <c r="D12" s="25">
         <f>Assumptions!D19*Assumptions!D20*Assumptions!D6</f>
         <v/>
       </c>
-      <c r="E11" s="14" t="inlineStr">
+      <c r="E12" s="14" t="inlineStr">
         <is>
           <t>₹0 until a brand signs</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="26" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="26" t="inlineStr">
         <is>
           <t>TOTAL REVENUE</t>
         </is>
       </c>
-      <c r="B12" s="27">
-        <f>SUM(B6:B11)</f>
-        <v/>
-      </c>
-      <c r="C12" s="27">
-        <f>SUM(C6:C11)</f>
-        <v/>
-      </c>
-      <c r="D12" s="27">
-        <f>SUM(D6:D11)</f>
-        <v/>
-      </c>
-      <c r="E12" s="28" t="inlineStr"/>
+      <c r="B13" s="27">
+        <f>SUM(B6:B12)</f>
+        <v/>
+      </c>
+      <c r="C13" s="27">
+        <f>SUM(C6:C12)</f>
+        <v/>
+      </c>
+      <c r="D13" s="27">
+        <f>SUM(D6:D12)</f>
+        <v/>
+      </c>
+      <c r="E13" s="28" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>NON-REWARD COSTS</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="n"/>
-      <c r="C14" s="10" t="n"/>
-      <c r="D14" s="10" t="n"/>
-      <c r="E14" s="10" t="n"/>
+      <c r="A14" s="29" t="inlineStr">
+        <is>
+          <t>of which AD REVENUE</t>
+        </is>
+      </c>
+      <c r="B14" s="30">
+        <f>SUM(B6:B9)</f>
+        <v/>
+      </c>
+      <c r="C14" s="30">
+        <f>SUM(C6:C9)</f>
+        <v/>
+      </c>
+      <c r="D14" s="30">
+        <f>SUM(D6:D9)</f>
+        <v/>
+      </c>
+      <c r="E14" s="14" t="inlineStr">
+        <is>
+          <t>THE ONLY LINE THE USER IS PAID FROM. Survey revenue is retained.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>UPI payout fees</t>
-        </is>
-      </c>
-      <c r="B15" s="25">
-        <f>Assumptions!B27*Assumptions!B28*(1-Assumptions!B24)</f>
-        <v/>
-      </c>
-      <c r="C15" s="25">
-        <f>Assumptions!C27*Assumptions!C28*(1-Assumptions!C24)</f>
-        <v/>
-      </c>
-      <c r="D15" s="25">
-        <f>Assumptions!D27*Assumptions!D28*(1-Assumptions!D24)</f>
+          <t>Rewarded views credited per active day</t>
+        </is>
+      </c>
+      <c r="B15" s="31">
+        <f>MIN(Assumptions!B9+Assumptions!B44*Assumptions!B43,Assumptions!B50)</f>
+        <v/>
+      </c>
+      <c r="C15" s="31">
+        <f>MIN(Assumptions!C9+Assumptions!C44*Assumptions!C43,Assumptions!C50)</f>
+        <v/>
+      </c>
+      <c r="D15" s="31">
+        <f>MIN(Assumptions!D9+Assumptions!D44*Assumptions!D43,Assumptions!D50)</f>
         <v/>
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>Only non-breakage users trigger a payout</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="11" t="inlineStr">
-        <is>
-          <t>Infrastructure</t>
-        </is>
-      </c>
-      <c r="B16" s="25">
-        <f>Assumptions!B29</f>
-        <v/>
-      </c>
-      <c r="C16" s="25">
-        <f>Assumptions!C29</f>
-        <v/>
-      </c>
-      <c r="D16" s="25">
-        <f>Assumptions!D29</f>
-        <v/>
-      </c>
-      <c r="E16" s="14" t="inlineStr"/>
+          <t>Bounded by the daily ceiling, Assumptions row 50</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>SMS / OTP</t>
-        </is>
-      </c>
-      <c r="B17" s="25">
-        <f>Assumptions!B30</f>
-        <v/>
-      </c>
-      <c r="C17" s="25">
-        <f>Assumptions!C30</f>
-        <v/>
-      </c>
-      <c r="D17" s="25">
-        <f>Assumptions!D30</f>
-        <v/>
-      </c>
-      <c r="E17" s="14" t="inlineStr"/>
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>WHAT THE USER EARNS — a share of revenue that has ALREADY ARRIVED</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="n"/>
+      <c r="C17" s="10" t="n"/>
+      <c r="D17" s="10" t="n"/>
+      <c r="E17" s="10" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>Support</t>
-        </is>
-      </c>
-      <c r="B18" s="25">
-        <f>Assumptions!B31</f>
-        <v/>
-      </c>
-      <c r="C18" s="25">
-        <f>Assumptions!C31</f>
-        <v/>
-      </c>
-      <c r="D18" s="25">
-        <f>Assumptions!D31</f>
+          <t>Share, days 1–6</t>
+        </is>
+      </c>
+      <c r="B18" s="32">
+        <f>Assumptions!B46</f>
+        <v/>
+      </c>
+      <c r="C18" s="32">
+        <f>Assumptions!C46</f>
+        <v/>
+      </c>
+      <c r="D18" s="32">
+        <f>Assumptions!D46</f>
         <v/>
       </c>
       <c r="E18" s="14" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="26" t="inlineStr">
-        <is>
-          <t>TOTAL NON-REWARD COST</t>
-        </is>
-      </c>
-      <c r="B19" s="27">
-        <f>SUM(B15:B18)</f>
-        <v/>
-      </c>
-      <c r="C19" s="27">
-        <f>SUM(C15:C18)</f>
-        <v/>
-      </c>
-      <c r="D19" s="27">
-        <f>SUM(D15:D18)</f>
-        <v/>
-      </c>
-      <c r="E19" s="28" t="inlineStr"/>
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>Share, day 7+ streak</t>
+        </is>
+      </c>
+      <c r="B19" s="32">
+        <f>Assumptions!B47</f>
+        <v/>
+      </c>
+      <c r="C19" s="32">
+        <f>Assumptions!C47</f>
+        <v/>
+      </c>
+      <c r="D19" s="32">
+        <f>Assumptions!D47</f>
+        <v/>
+      </c>
+      <c r="E19" s="14" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>Share, day 30+ streak</t>
+        </is>
+      </c>
+      <c r="B20" s="32">
+        <f>Assumptions!B48</f>
+        <v/>
+      </c>
+      <c r="C20" s="32">
+        <f>Assumptions!C48</f>
+        <v/>
+      </c>
+      <c r="D20" s="32">
+        <f>Assumptions!D48</f>
+        <v/>
+      </c>
+      <c r="E20" s="14" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>REWARD BUDGET</t>
-        </is>
-      </c>
-      <c r="B21" s="10" t="n"/>
-      <c r="C21" s="10" t="n"/>
-      <c r="D21" s="10" t="n"/>
-      <c r="E21" s="10" t="n"/>
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>User earns, days 1–6</t>
+        </is>
+      </c>
+      <c r="B21" s="25">
+        <f>B14*B18</f>
+        <v/>
+      </c>
+      <c r="C21" s="25">
+        <f>C14*C18</f>
+        <v/>
+      </c>
+      <c r="D21" s="25">
+        <f>D14*D18</f>
+        <v/>
+      </c>
+      <c r="E21" s="14" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>Target profit retained</t>
+          <t>User earns, day 7+</t>
         </is>
       </c>
       <c r="B22" s="25">
-        <f>B12*Assumptions!B34</f>
+        <f>B14*B19</f>
         <v/>
       </c>
       <c r="C22" s="25">
-        <f>C12*Assumptions!C34</f>
+        <f>C14*C19</f>
         <v/>
       </c>
       <c r="D22" s="25">
-        <f>D12*Assumptions!D34</f>
+        <f>D14*D19</f>
         <v/>
       </c>
       <c r="E22" s="14" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="29" t="inlineStr">
-        <is>
-          <t>Budget available for rewards</t>
-        </is>
-      </c>
-      <c r="B23" s="30">
-        <f>B12-B19-B22</f>
-        <v/>
-      </c>
-      <c r="C23" s="30">
-        <f>C12-C19-C22</f>
-        <v/>
-      </c>
-      <c r="D23" s="30">
-        <f>D12-D19-D22</f>
-        <v/>
-      </c>
-      <c r="E23" s="14" t="inlineStr">
-        <is>
-          <t>Revenue less non-reward cost less target profit</t>
+      <c r="A23" s="26" t="inlineStr">
+        <is>
+          <t>User earns, day 30+</t>
+        </is>
+      </c>
+      <c r="B23" s="27">
+        <f>B14*B20</f>
+        <v/>
+      </c>
+      <c r="C23" s="27">
+        <f>C14*C20</f>
+        <v/>
+      </c>
+      <c r="D23" s="27">
+        <f>D14*D20</f>
+        <v/>
+      </c>
+      <c r="E23" s="28" t="inlineStr">
+        <is>
+          <t>The most a streak user can earn — and the worst case for the business</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="inlineStr">
-        <is>
-          <t>Breakage factor (share actually paid)</t>
-        </is>
-      </c>
-      <c r="B24" s="31">
-        <f>1-Assumptions!B24</f>
-        <v/>
-      </c>
-      <c r="C24" s="31">
-        <f>1-Assumptions!C24</f>
-        <v/>
-      </c>
-      <c r="D24" s="31">
-        <f>1-Assumptions!D24</f>
-        <v/>
-      </c>
-      <c r="E24" s="14" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>Fraud inflation factor</t>
-        </is>
-      </c>
-      <c r="B25" s="32">
-        <f>1+Assumptions!B32</f>
-        <v/>
-      </c>
-      <c r="C25" s="32">
-        <f>1+Assumptions!C32</f>
-        <v/>
-      </c>
-      <c r="D25" s="32">
-        <f>1+Assumptions!D32</f>
-        <v/>
-      </c>
-      <c r="E25" s="14" t="inlineStr"/>
+      <c r="A24" s="29" t="inlineStr">
+        <is>
+          <t>Per active day at day 30+</t>
+        </is>
+      </c>
+      <c r="B24" s="30">
+        <f>B23/Assumptions!B6</f>
+        <v/>
+      </c>
+      <c r="C24" s="30">
+        <f>C23/Assumptions!C6</f>
+        <v/>
+      </c>
+      <c r="D24" s="30">
+        <f>D23/Assumptions!D6</f>
+        <v/>
+      </c>
+      <c r="E24" s="14" t="inlineStr">
+        <is>
+          <t>What the Daily Close shows</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="26" t="inlineStr">
-        <is>
-          <t>SUSTAINABLE EARNING CAP</t>
-        </is>
-      </c>
-      <c r="B26" s="27">
-        <f>B23/(B24*B25)</f>
-        <v/>
-      </c>
-      <c r="C26" s="27">
-        <f>C23/(C24*C25)</f>
-        <v/>
-      </c>
-      <c r="D26" s="27">
-        <f>D23/(D24*D25)</f>
-        <v/>
-      </c>
-      <c r="E26" s="28" t="inlineStr">
-        <is>
-          <t>Maximum a single user may accrue per month</t>
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>NON-REWARD COSTS</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="n"/>
+      <c r="C26" s="10" t="n"/>
+      <c r="D26" s="10" t="n"/>
+      <c r="E26" s="10" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>UPI payout fees</t>
+        </is>
+      </c>
+      <c r="B27" s="25">
+        <f>Assumptions!B27*Assumptions!B28*(1-Assumptions!B24)</f>
+        <v/>
+      </c>
+      <c r="C27" s="25">
+        <f>Assumptions!C27*Assumptions!C28*(1-Assumptions!C24)</f>
+        <v/>
+      </c>
+      <c r="D27" s="25">
+        <f>Assumptions!D27*Assumptions!D28*(1-Assumptions!D24)</f>
+        <v/>
+      </c>
+      <c r="E27" s="14" t="inlineStr">
+        <is>
+          <t>Only non-breakage users trigger a payout</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>WHAT THE ₹10 FIRST PAYOUT COSTS</t>
-        </is>
-      </c>
-      <c r="B28" s="10" t="n"/>
-      <c r="C28" s="10" t="n"/>
-      <c r="D28" s="10" t="n"/>
-      <c r="E28" s="10" t="n"/>
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="B28" s="25">
+        <f>Assumptions!B29</f>
+        <v/>
+      </c>
+      <c r="C28" s="25">
+        <f>Assumptions!C29</f>
+        <v/>
+      </c>
+      <c r="D28" s="25">
+        <f>Assumptions!D29</f>
+        <v/>
+      </c>
+      <c r="E28" s="14" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>Cap under v0.2 (₹30 first payout)</t>
+          <t>SMS / OTP</t>
         </is>
       </c>
       <c r="B29" s="25">
-        <f>(B12-(Assumptions!B27*Assumptions!B28*(1-Assumptions!B25)+Assumptions!B29+Assumptions!B30+Assumptions!B31)-B22)/((1-Assumptions!B25)*B25)</f>
+        <f>Assumptions!B30</f>
         <v/>
       </c>
       <c r="C29" s="25">
-        <f>(C12-(Assumptions!C27*Assumptions!C28*(1-Assumptions!C25)+Assumptions!C29+Assumptions!C30+Assumptions!C31)-C22)/((1-Assumptions!C25)*C25)</f>
+        <f>Assumptions!C30</f>
         <v/>
       </c>
       <c r="D29" s="25">
-        <f>(D12-(Assumptions!D27*Assumptions!D28*(1-Assumptions!D25)+Assumptions!D29+Assumptions!D30+Assumptions!D31)-D22)/((1-Assumptions!D25)*D25)</f>
-        <v/>
-      </c>
-      <c r="E29" s="14" t="inlineStr">
-        <is>
-          <t>Same revenue, the higher v0.2 breakage assumption</t>
-        </is>
-      </c>
+        <f>Assumptions!D30</f>
+        <v/>
+      </c>
+      <c r="E29" s="14" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="29" t="inlineStr">
-        <is>
-          <t>Cap reduction from the ₹10 decision</t>
-        </is>
-      </c>
-      <c r="B30" s="30">
-        <f>B26-B29</f>
-        <v/>
-      </c>
-      <c r="C30" s="30">
-        <f>C26-C29</f>
-        <v/>
-      </c>
-      <c r="D30" s="30">
-        <f>D26-D29</f>
-        <v/>
-      </c>
-      <c r="E30" s="14" t="inlineStr">
-        <is>
-          <t>Negative means the ₹10 first payout costs cap headroom</t>
-        </is>
-      </c>
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="B30" s="25">
+        <f>Assumptions!B31</f>
+        <v/>
+      </c>
+      <c r="C30" s="25">
+        <f>Assumptions!C31</f>
+        <v/>
+      </c>
+      <c r="D30" s="25">
+        <f>Assumptions!D31</f>
+        <v/>
+      </c>
+      <c r="E30" s="14" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="29" t="inlineStr">
-        <is>
-          <t>Reduction as % of the v0.2 cap</t>
-        </is>
-      </c>
-      <c r="B31" s="33">
-        <f>IF(B29=0,0,B30/B29)</f>
-        <v/>
-      </c>
-      <c r="C31" s="33">
-        <f>IF(C29=0,0,C30/C29)</f>
-        <v/>
-      </c>
-      <c r="D31" s="33">
-        <f>IF(D29=0,0,D30/D29)</f>
-        <v/>
-      </c>
-      <c r="E31" s="14" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="22" t="inlineStr">
-        <is>
-          <t>ACQUISITION — separate book, NOT charged to the reward budget</t>
-        </is>
-      </c>
-      <c r="B33" s="23" t="n"/>
-      <c r="C33" s="23" t="n"/>
-      <c r="D33" s="23" t="n"/>
-      <c r="E33" s="23" t="n"/>
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>Fraud leakage on rewards</t>
+        </is>
+      </c>
+      <c r="B31" s="25">
+        <f>B23*Assumptions!B32</f>
+        <v/>
+      </c>
+      <c r="C31" s="25">
+        <f>C23*Assumptions!C32</f>
+        <v/>
+      </c>
+      <c r="D31" s="25">
+        <f>D23*Assumptions!D32</f>
+        <v/>
+      </c>
+      <c r="E31" s="14" t="inlineStr">
+        <is>
+          <t>Costed at the worst-case share</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="26" t="inlineStr">
+        <is>
+          <t>TOTAL NON-REWARD COST</t>
+        </is>
+      </c>
+      <c r="B32" s="27">
+        <f>SUM(B27:B31)</f>
+        <v/>
+      </c>
+      <c r="C32" s="27">
+        <f>SUM(C27:C31)</f>
+        <v/>
+      </c>
+      <c r="D32" s="27">
+        <f>SUM(D27:D31)</f>
+        <v/>
+      </c>
+      <c r="E32" s="28" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="34" t="inlineStr">
-        <is>
-          <t>First payout, cash</t>
-        </is>
-      </c>
-      <c r="B34" s="35">
-        <f>Assumptions!B22</f>
-        <v/>
-      </c>
-      <c r="C34" s="35">
-        <f>Assumptions!C22</f>
-        <v/>
-      </c>
-      <c r="D34" s="35">
-        <f>Assumptions!D22</f>
-        <v/>
-      </c>
-      <c r="E34" s="36" t="inlineStr"/>
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>PROFIT — THIS IS THE LINE THAT MUST NEVER GO NEGATIVE</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="n"/>
+      <c r="C34" s="10" t="n"/>
+      <c r="D34" s="10" t="n"/>
+      <c r="E34" s="10" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="34" t="inlineStr">
-        <is>
-          <t>First payout, transaction fee</t>
-        </is>
-      </c>
-      <c r="B35" s="35">
-        <f>Assumptions!B27</f>
-        <v/>
-      </c>
-      <c r="C35" s="35">
-        <f>Assumptions!C27</f>
-        <v/>
-      </c>
-      <c r="D35" s="35">
-        <f>Assumptions!D27</f>
-        <v/>
-      </c>
-      <c r="E35" s="36" t="inlineStr"/>
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>Ad revenue retained</t>
+        </is>
+      </c>
+      <c r="B35" s="25">
+        <f>B14-B23</f>
+        <v/>
+      </c>
+      <c r="C35" s="25">
+        <f>C14-C23</f>
+        <v/>
+      </c>
+      <c r="D35" s="25">
+        <f>D14-D23</f>
+        <v/>
+      </c>
+      <c r="E35" s="14" t="inlineStr">
+        <is>
+          <t>The half not paid out, at the worst-case share</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="22" t="inlineStr">
-        <is>
-          <t>Total first-payout cost per converting user</t>
-        </is>
-      </c>
-      <c r="B36" s="37">
-        <f>B34+B35</f>
-        <v/>
-      </c>
-      <c r="C36" s="37">
-        <f>C34+C35</f>
-        <v/>
-      </c>
-      <c r="D36" s="37">
-        <f>D34+D35</f>
-        <v/>
-      </c>
-      <c r="E36" s="36" t="inlineStr"/>
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>Survey revenue retained</t>
+        </is>
+      </c>
+      <c r="B36" s="25">
+        <f>B10+B11</f>
+        <v/>
+      </c>
+      <c r="C36" s="25">
+        <f>C10+C11</f>
+        <v/>
+      </c>
+      <c r="D36" s="25">
+        <f>D10+D11</f>
+        <v/>
+      </c>
+      <c r="E36" s="14" t="inlineStr">
+        <is>
+          <t>Entirely retained — never shared</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="34" t="inlineStr">
-        <is>
-          <t>Blended across all installs</t>
-        </is>
-      </c>
-      <c r="B37" s="35">
-        <f>B36*Assumptions!B36</f>
-        <v/>
-      </c>
-      <c r="C37" s="35">
-        <f>C36*Assumptions!C36</f>
-        <v/>
-      </c>
-      <c r="D37" s="35">
-        <f>D36*Assumptions!D36</f>
-        <v/>
-      </c>
-      <c r="E37" s="36" t="inlineStr">
-        <is>
-          <t>Only users who reach the threshold cost you this</t>
+      <c r="A37" s="26" t="inlineStr">
+        <is>
+          <t>PROFIT PER ACTIVE USER PER MONTH</t>
+        </is>
+      </c>
+      <c r="B37" s="27">
+        <f>B35+B36-B32</f>
+        <v/>
+      </c>
+      <c r="C37" s="27">
+        <f>C35+C36-C32</f>
+        <v/>
+      </c>
+      <c r="D37" s="27">
+        <f>D35+D36-D32</f>
+        <v/>
+      </c>
+      <c r="E37" s="28" t="inlineStr">
+        <is>
+          <t>Worst case: every user on the 60% streak share</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="34" t="inlineStr">
-        <is>
-          <t>Paid install cost (CPI) benchmark</t>
-        </is>
-      </c>
-      <c r="B38" s="35">
-        <f>Assumptions!B38</f>
-        <v/>
-      </c>
-      <c r="C38" s="35">
-        <f>Assumptions!C38</f>
-        <v/>
-      </c>
-      <c r="D38" s="35">
-        <f>Assumptions!D38</f>
-        <v/>
-      </c>
-      <c r="E38" s="36" t="inlineStr"/>
+      <c r="A38" s="29" t="inlineStr">
+        <is>
+          <t>Margin on total revenue</t>
+        </is>
+      </c>
+      <c r="B38" s="33">
+        <f>IF(B13=0,0,B37/B13)</f>
+        <v/>
+      </c>
+      <c r="C38" s="33">
+        <f>IF(C13=0,0,C37/C13)</f>
+        <v/>
+      </c>
+      <c r="D38" s="33">
+        <f>IF(D13=0,0,D37/D13)</f>
+        <v/>
+      </c>
+      <c r="E38" s="14" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="22" t="inlineStr">
-        <is>
-          <t>First payout as % of a paid install</t>
-        </is>
-      </c>
-      <c r="B39" s="38">
-        <f>IF(B38=0,0,B37/B38)</f>
-        <v/>
-      </c>
-      <c r="C39" s="38">
-        <f>IF(C38=0,0,C37/C38)</f>
-        <v/>
-      </c>
-      <c r="D39" s="38">
-        <f>IF(D38=0,0,D37/D38)</f>
-        <v/>
-      </c>
-      <c r="E39" s="36" t="inlineStr">
-        <is>
-          <t>Under 100% means it buys a paid, retained user cheaper than an ad buys a raw install</t>
+      <c r="A39" s="26" t="inlineStr">
+        <is>
+          <t>SAFE?</t>
+        </is>
+      </c>
+      <c r="B39" s="26">
+        <f>IF(B37&gt;0,"YES — profitable at the highest share","NO — DO NOT SHIP")</f>
+        <v/>
+      </c>
+      <c r="C39" s="26">
+        <f>IF(C37&gt;0,"YES — profitable at the highest share","NO — DO NOT SHIP")</f>
+        <v/>
+      </c>
+      <c r="D39" s="26">
+        <f>IF(D37&gt;0,"YES — profitable at the highest share","NO — DO NOT SHIP")</f>
+        <v/>
+      </c>
+      <c r="E39" s="28" t="inlineStr">
+        <is>
+          <t>Must read YES in all three columns. This is the release gate.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="34" t="inlineStr">
-        <is>
-          <t>Amortised over expected lifetime</t>
-        </is>
-      </c>
-      <c r="B40" s="35">
-        <f>B37/Assumptions!B16</f>
-        <v/>
-      </c>
-      <c r="C40" s="35">
-        <f>C37/Assumptions!C16</f>
-        <v/>
-      </c>
-      <c r="D40" s="35">
-        <f>D37/Assumptions!D16</f>
-        <v/>
-      </c>
-      <c r="E40" s="36" t="inlineStr">
-        <is>
-          <t>Monthly equivalent, for comparison against revenue only</t>
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>Headroom before a loss</t>
+        </is>
+      </c>
+      <c r="B40" s="32">
+        <f>IF(B14=0,0,B37/B14)</f>
+        <v/>
+      </c>
+      <c r="C40" s="32">
+        <f>IF(C14=0,0,C37/C14)</f>
+        <v/>
+      </c>
+      <c r="D40" s="32">
+        <f>IF(D14=0,0,D37/D14)</f>
+        <v/>
+      </c>
+      <c r="E40" s="14" t="inlineStr">
+        <is>
+          <t>How much further the share could rise before profit hits zero</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>REALITY CHECK vs THE ORIGINAL ₹95 DESIGN</t>
+          <t>WHY THIS CANNOT LOSE MONEY THE WAY EARLIER VERSIONS COULD</t>
         </is>
       </c>
       <c r="B42" s="10" t="n"/>
@@ -2739,65 +3137,307 @@
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
         <is>
-          <t>Original design cap (₹60 math + ₹30 streak + ₹5 signup)</t>
-        </is>
-      </c>
-      <c r="B43" s="20" t="n">
-        <v>95</v>
-      </c>
-      <c r="C43" s="20" t="n">
-        <v>95</v>
-      </c>
-      <c r="D43" s="20" t="n">
-        <v>95</v>
-      </c>
-      <c r="E43" s="24" t="inlineStr">
-        <is>
-          <t>The concept as first specified</t>
+          <t>Payout if eCPM halved</t>
+        </is>
+      </c>
+      <c r="B43" s="25">
+        <f>B23/2</f>
+        <v/>
+      </c>
+      <c r="C43" s="25">
+        <f>C23/2</f>
+        <v/>
+      </c>
+      <c r="D43" s="25">
+        <f>D23/2</f>
+        <v/>
+      </c>
+      <c r="E43" s="14" t="inlineStr">
+        <is>
+          <t>Payout falls with revenue automatically — no renegotiation, no broken promise</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="29" t="inlineStr">
         <is>
-          <t>Sustainable cap as % of original</t>
-        </is>
-      </c>
-      <c r="B44" s="33">
-        <f>B26/B43</f>
-        <v/>
-      </c>
-      <c r="C44" s="33">
-        <f>C26/C43</f>
-        <v/>
-      </c>
-      <c r="D44" s="33">
-        <f>D26/D43</f>
-        <v/>
-      </c>
-      <c r="E44" s="14" t="inlineStr"/>
+          <t>Profit if eCPM halved</t>
+        </is>
+      </c>
+      <c r="B44" s="30">
+        <f>(B14/2)-(B23/2)+B36-B32</f>
+        <v/>
+      </c>
+      <c r="C44" s="30">
+        <f>(C14/2)-(C23/2)+C36-C32</f>
+        <v/>
+      </c>
+      <c r="D44" s="30">
+        <f>(D14/2)-(D23/2)+D36-D32</f>
+        <v/>
+      </c>
+      <c r="E44" s="14" t="inlineStr">
+        <is>
+          <t>Still positive: the share is a fraction of whatever actually arrives</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="29" t="inlineStr">
-        <is>
-          <t>Monthly loss per user at the original cap</t>
-        </is>
-      </c>
-      <c r="B45" s="30">
-        <f>B12-B19-(B43*B24*B25)</f>
-        <v/>
-      </c>
-      <c r="C45" s="30">
-        <f>C12-C19-(C43*C24*C25)</f>
-        <v/>
-      </c>
-      <c r="D45" s="30">
-        <f>D12-D19-(D43*D24*D25)</f>
+      <c r="A45" s="11" t="inlineStr">
+        <is>
+          <t>Payout if fill dropped to zero</t>
+        </is>
+      </c>
+      <c r="B45" s="25">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="C45" s="25">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="D45" s="25">
+        <f>0</f>
         <v/>
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
-          <t>Contribution per user if ₹95 shipped unchanged</t>
+          <t>No ad served, nothing credited, nothing owed</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="22" t="inlineStr">
+        <is>
+          <t>ACQUISITION — separate book, NOT charged against the share</t>
+        </is>
+      </c>
+      <c r="B47" s="23" t="n"/>
+      <c r="C47" s="23" t="n"/>
+      <c r="D47" s="23" t="n"/>
+      <c r="E47" s="23" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="34" t="inlineStr">
+        <is>
+          <t>First payout, cash</t>
+        </is>
+      </c>
+      <c r="B48" s="35">
+        <f>Assumptions!B22</f>
+        <v/>
+      </c>
+      <c r="C48" s="35">
+        <f>Assumptions!C22</f>
+        <v/>
+      </c>
+      <c r="D48" s="35">
+        <f>Assumptions!D22</f>
+        <v/>
+      </c>
+      <c r="E48" s="36" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="34" t="inlineStr">
+        <is>
+          <t>First payout, transaction fee</t>
+        </is>
+      </c>
+      <c r="B49" s="35">
+        <f>Assumptions!B27</f>
+        <v/>
+      </c>
+      <c r="C49" s="35">
+        <f>Assumptions!C27</f>
+        <v/>
+      </c>
+      <c r="D49" s="35">
+        <f>Assumptions!D27</f>
+        <v/>
+      </c>
+      <c r="E49" s="36" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="22" t="inlineStr">
+        <is>
+          <t>Total first-payout cost per converting user</t>
+        </is>
+      </c>
+      <c r="B50" s="37">
+        <f>B48+B49</f>
+        <v/>
+      </c>
+      <c r="C50" s="37">
+        <f>C48+C49</f>
+        <v/>
+      </c>
+      <c r="D50" s="37">
+        <f>D48+D49</f>
+        <v/>
+      </c>
+      <c r="E50" s="36" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="34" t="inlineStr">
+        <is>
+          <t>Blended across all installs</t>
+        </is>
+      </c>
+      <c r="B51" s="35">
+        <f>B50*Assumptions!B36</f>
+        <v/>
+      </c>
+      <c r="C51" s="35">
+        <f>C50*Assumptions!C36</f>
+        <v/>
+      </c>
+      <c r="D51" s="35">
+        <f>D50*Assumptions!D36</f>
+        <v/>
+      </c>
+      <c r="E51" s="36" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="34" t="inlineStr">
+        <is>
+          <t>Paid install cost (CPI) benchmark</t>
+        </is>
+      </c>
+      <c r="B52" s="35">
+        <f>Assumptions!B38</f>
+        <v/>
+      </c>
+      <c r="C52" s="35">
+        <f>Assumptions!C38</f>
+        <v/>
+      </c>
+      <c r="D52" s="35">
+        <f>Assumptions!D38</f>
+        <v/>
+      </c>
+      <c r="E52" s="36" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="22" t="inlineStr">
+        <is>
+          <t>First payout as % of a paid install</t>
+        </is>
+      </c>
+      <c r="B53" s="38">
+        <f>IF(B52=0,0,B51/B52)</f>
+        <v/>
+      </c>
+      <c r="C53" s="38">
+        <f>IF(C52=0,0,C51/C52)</f>
+        <v/>
+      </c>
+      <c r="D53" s="38">
+        <f>IF(D52=0,0,D51/D52)</f>
+        <v/>
+      </c>
+      <c r="E53" s="36" t="inlineStr">
+        <is>
+          <t>Under 100% means it buys a paid, retained user cheaper than an ad buys a raw install</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="34" t="inlineStr">
+        <is>
+          <t>Days to reach the first payout at the boosted share</t>
+        </is>
+      </c>
+      <c r="B54" s="39">
+        <f>IF(B14=0,0,Assumptions!B22/((B14*Assumptions!B49)/Assumptions!B6))</f>
+        <v/>
+      </c>
+      <c r="C54" s="39">
+        <f>IF(C14=0,0,Assumptions!C22/((C14*Assumptions!C49)/Assumptions!C6))</f>
+        <v/>
+      </c>
+      <c r="D54" s="39">
+        <f>IF(D14=0,0,Assumptions!D22/((D14*Assumptions!D49)/Assumptions!D6))</f>
+        <v/>
+      </c>
+      <c r="E54" s="36" t="inlineStr">
+        <is>
+          <t>70% share until the first ₹10 — booked as acquisition, not reward</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="9" t="inlineStr">
+        <is>
+          <t>REALITY CHECK vs THE ORIGINAL ₹95 DESIGN</t>
+        </is>
+      </c>
+      <c r="B56" s="10" t="n"/>
+      <c r="C56" s="10" t="n"/>
+      <c r="D56" s="10" t="n"/>
+      <c r="E56" s="10" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="11" t="inlineStr">
+        <is>
+          <t>Original design payout (₹60 math + ₹30 streak + ₹5 signup)</t>
+        </is>
+      </c>
+      <c r="B57" s="20" t="n">
+        <v>95</v>
+      </c>
+      <c r="C57" s="20" t="n">
+        <v>95</v>
+      </c>
+      <c r="D57" s="20" t="n">
+        <v>95</v>
+      </c>
+      <c r="E57" s="24" t="inlineStr">
+        <is>
+          <t>A fixed promise made against variable revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="29" t="inlineStr">
+        <is>
+          <t>What the share pays instead</t>
+        </is>
+      </c>
+      <c r="B58" s="30">
+        <f>B23</f>
+        <v/>
+      </c>
+      <c r="C58" s="30">
+        <f>C23</f>
+        <v/>
+      </c>
+      <c r="D58" s="30">
+        <f>D23</f>
+        <v/>
+      </c>
+      <c r="E58" s="14" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="29" t="inlineStr">
+        <is>
+          <t>Monthly loss per user had ₹95 shipped</t>
+        </is>
+      </c>
+      <c r="B59" s="30">
+        <f>B13-B32-B57</f>
+        <v/>
+      </c>
+      <c r="C59" s="30">
+        <f>C13-C32-C57</f>
+        <v/>
+      </c>
+      <c r="D59" s="30">
+        <f>D13-D32-D57</f>
+        <v/>
+      </c>
+      <c r="E59" s="14" t="inlineStr">
+        <is>
+          <t>The failure mode this design removes entirely</t>
         </is>
       </c>
     </row>
@@ -2812,7 +3452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -2825,45 +3465,45 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Monthly P&amp;L at scale — Base case</t>
+          <t>Monthly P&amp;L at scale — Base case, revenue-share model</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="24" t="inlineStr">
         <is>
-          <t>Set the cap you intend to ship in the yellow cell. Acquisition is shown separately.</t>
+          <t>There is no cap to set. The payout is a share of ad revenue that has already arrived.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Earning cap to test</t>
-        </is>
-      </c>
-      <c r="B4" s="39" t="n">
-        <v>15</v>
+          <t>User share to test</t>
+        </is>
+      </c>
+      <c r="B4" s="40" t="n">
+        <v>0.6</v>
       </c>
       <c r="C4" s="24" t="inlineStr">
         <is>
-          <t>₹ per user per month</t>
+          <t>Worst case — every user on the 30-day streak tier</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sustainable cap (Base, from Model)</t>
-        </is>
-      </c>
-      <c r="B5" s="40">
-        <f>Model!C26</f>
+          <t>Ad revenue per active user (Base, from Model)</t>
+        </is>
+      </c>
+      <c r="B5" s="41">
+        <f>Model!C14</f>
         <v/>
       </c>
       <c r="C5" s="24" t="inlineStr">
         <is>
-          <t>Ship at or below this</t>
+          <t>The only line the share is taken from</t>
         </is>
       </c>
     </row>
@@ -2873,7 +3513,7 @@
           <t>New-user share (drives acquisition cost)</t>
         </is>
       </c>
-      <c r="B6" s="41" t="n">
+      <c r="B6" s="40" t="n">
         <v>0.25</v>
       </c>
       <c r="C6" s="24" t="inlineStr">
@@ -2923,19 +3563,19 @@
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Total revenue</t>
         </is>
       </c>
       <c r="B10" s="45">
-        <f>B9*Model!$C$12</f>
+        <f>B9*Model!$C$13</f>
         <v/>
       </c>
       <c r="C10" s="45">
-        <f>C9*Model!$C$12</f>
+        <f>C9*Model!$C$13</f>
         <v/>
       </c>
       <c r="D10" s="45">
-        <f>D9*Model!$C$12</f>
+        <f>D9*Model!$C$13</f>
         <v/>
       </c>
       <c r="E10" s="24" t="inlineStr"/>
@@ -2943,39 +3583,43 @@
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>Non-reward costs</t>
+          <t>User payout — share of ad revenue</t>
         </is>
       </c>
       <c r="B11" s="45">
-        <f>-B9*Model!$C$19</f>
+        <f>-B9*Model!$C$14*$B$4</f>
         <v/>
       </c>
       <c r="C11" s="45">
-        <f>-C9*Model!$C$19</f>
+        <f>-C9*Model!$C$14*$B$4</f>
         <v/>
       </c>
       <c r="D11" s="45">
-        <f>-D9*Model!$C$19</f>
-        <v/>
-      </c>
-      <c r="E11" s="24" t="inlineStr"/>
+        <f>-D9*Model!$C$14*$B$4</f>
+        <v/>
+      </c>
+      <c r="E11" s="24" t="inlineStr">
+        <is>
+          <t>Falls automatically if eCPM or fill falls. Cannot exceed what arrived.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>Reward payout at the tested cap</t>
+          <t>Non-reward costs</t>
         </is>
       </c>
       <c r="B12" s="45">
-        <f>-B9*$B$4*Model!$C$24*Model!$C$25</f>
+        <f>-B9*Model!$C$32</f>
         <v/>
       </c>
       <c r="C12" s="45">
-        <f>-C9*$B$4*Model!$C$24*Model!$C$25</f>
+        <f>-C9*Model!$C$32</f>
         <v/>
       </c>
       <c r="D12" s="45">
-        <f>-D9*$B$4*Model!$C$24*Model!$C$25</f>
+        <f>-D9*Model!$C$32</f>
         <v/>
       </c>
       <c r="E12" s="24" t="inlineStr"/>
@@ -3007,15 +3651,15 @@
         </is>
       </c>
       <c r="B14" s="47">
-        <f>-B9*$B$6*Model!$C$37</f>
+        <f>-B9*$B$6*Model!$C$51</f>
         <v/>
       </c>
       <c r="C14" s="47">
-        <f>-C9*$B$6*Model!$C$37</f>
+        <f>-C9*$B$6*Model!$C$51</f>
         <v/>
       </c>
       <c r="D14" s="47">
-        <f>-D9*$B$6*Model!$C$37</f>
+        <f>-D9*$B$6*Model!$C$51</f>
         <v/>
       </c>
       <c r="E14" s="24" t="inlineStr">
@@ -3064,27 +3708,111 @@
       </c>
       <c r="E16" s="24" t="inlineStr"/>
     </row>
-    <row r="18">
-      <c r="A18" s="29" t="inlineStr">
-        <is>
-          <t>Contribution at the ORIGINAL ₹95 cap</t>
-        </is>
-      </c>
-      <c r="B18" s="49">
-        <f>B9*Model!$C$12-B9*Model!$C$19-B9*Model!$C$43*Model!$C$24*Model!$C$25</f>
-        <v/>
-      </c>
-      <c r="C18" s="49">
-        <f>C9*Model!$C$12-C9*Model!$C$19-C9*Model!$C$43*Model!$C$24*Model!$C$25</f>
-        <v/>
-      </c>
-      <c r="D18" s="49">
-        <f>D9*Model!$C$12-D9*Model!$C$19-D9*Model!$C$43*Model!$C$24*Model!$C$25</f>
-        <v/>
-      </c>
-      <c r="E18" s="24" t="inlineStr">
-        <is>
-          <t>What shipping the original design would cost monthly</t>
+    <row r="17">
+      <c r="A17" s="26" t="inlineStr">
+        <is>
+          <t>SAFE AT SCALE?</t>
+        </is>
+      </c>
+      <c r="B17" s="26">
+        <f>IF(B15&gt;0,"YES","NO — DO NOT SHIP")</f>
+        <v/>
+      </c>
+      <c r="C17" s="26">
+        <f>IF(C15&gt;0,"YES","NO — DO NOT SHIP")</f>
+        <v/>
+      </c>
+      <c r="D17" s="26">
+        <f>IF(D15&gt;0,"YES","NO — DO NOT SHIP")</f>
+        <v/>
+      </c>
+      <c r="E17" s="24" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>If eCPM halved: revenue</t>
+        </is>
+      </c>
+      <c r="B19" s="45">
+        <f>B9*(Model!$C$13-Model!$C$14/2)</f>
+        <v/>
+      </c>
+      <c r="C19" s="45">
+        <f>C9*(Model!$C$13-Model!$C$14/2)</f>
+        <v/>
+      </c>
+      <c r="D19" s="45">
+        <f>D9*(Model!$C$13-Model!$C$14/2)</f>
+        <v/>
+      </c>
+      <c r="E19" s="24" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>If eCPM halved: user payout</t>
+        </is>
+      </c>
+      <c r="B20" s="45">
+        <f>-B9*(Model!$C$14/2)*$B$4</f>
+        <v/>
+      </c>
+      <c r="C20" s="45">
+        <f>-C9*(Model!$C$14/2)*$B$4</f>
+        <v/>
+      </c>
+      <c r="D20" s="45">
+        <f>-D9*(Model!$C$14/2)*$B$4</f>
+        <v/>
+      </c>
+      <c r="E20" s="24" t="inlineStr">
+        <is>
+          <t>The payout halves with it — this is the whole point</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="26" t="inlineStr">
+        <is>
+          <t>If eCPM halved: CONTRIBUTION</t>
+        </is>
+      </c>
+      <c r="B21" s="46">
+        <f>B19+B20-B9*Model!$C$32</f>
+        <v/>
+      </c>
+      <c r="C21" s="46">
+        <f>C19+C20-C9*Model!$C$32</f>
+        <v/>
+      </c>
+      <c r="D21" s="46">
+        <f>D19+D20-D9*Model!$C$32</f>
+        <v/>
+      </c>
+      <c r="E21" s="24" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="29" t="inlineStr">
+        <is>
+          <t>Contribution had the ORIGINAL ₹95 shipped</t>
+        </is>
+      </c>
+      <c r="B23" s="49">
+        <f>B9*Model!$C$13-B9*Model!$C$32-B9*Model!$C$57</f>
+        <v/>
+      </c>
+      <c r="C23" s="49">
+        <f>C9*Model!$C$13-C9*Model!$C$32-C9*Model!$C$57</f>
+        <v/>
+      </c>
+      <c r="D23" s="49">
+        <f>D9*Model!$C$13-D9*Model!$C$32-D9*Model!$C$57</f>
+        <v/>
+      </c>
+      <c r="E23" s="24" t="inlineStr">
+        <is>
+          <t>A fixed promise against variable revenue — the failure this removes</t>
         </is>
       </c>
     </row>
@@ -3116,392 +3844,392 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Contribution per user per month (before acquisition)</t>
+          <t>Profit per user per month — user share against ad revenue</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="24" t="inlineStr">
         <is>
-          <t>Rows = earning cap shipped. Columns = total revenue per active user. Base-case costs, breakage and fraud.</t>
+          <t>Rows = share paid to the user. Columns = ad revenue per active user. Base-case costs and survey revenue.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="24" t="inlineStr">
         <is>
-          <t>Bracketed values are losses on every active user at that combination.</t>
+          <t>Bracketed values are losses. The shipped share is 50-60%; note how much room sits above it.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>Cap \ Revenue</t>
+          <t>Share \ Ad revenue</t>
         </is>
       </c>
       <c r="B5" s="50" t="n">
+        <v>5</v>
+      </c>
+      <c r="C5" s="50" t="n">
         <v>10</v>
       </c>
-      <c r="C5" s="50" t="n">
+      <c r="D5" s="50" t="n">
         <v>15</v>
       </c>
-      <c r="D5" s="50" t="n">
+      <c r="E5" s="50" t="n">
         <v>20</v>
       </c>
-      <c r="E5" s="50" t="n">
+      <c r="F5" s="50" t="n">
         <v>25</v>
       </c>
-      <c r="F5" s="50" t="n">
+      <c r="G5" s="50" t="n">
         <v>30</v>
-      </c>
-      <c r="G5" s="50" t="n">
-        <v>35</v>
       </c>
       <c r="H5" s="50" t="n">
         <v>40</v>
       </c>
       <c r="I5" s="50" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="n">
-        <v>5</v>
+      <c r="A6" s="16" t="n">
+        <v>0.3</v>
       </c>
       <c r="B6" s="51">
-        <f>B$5-Model!$C$19-$A6*Model!$C$24*Model!$C$25</f>
+        <f>B$5*(1-$A6)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
       <c r="C6" s="51">
-        <f>C$5-Model!$C$19-$A6*Model!$C$24*Model!$C$25</f>
+        <f>C$5*(1-$A6)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
       <c r="D6" s="51">
-        <f>D$5-Model!$C$19-$A6*Model!$C$24*Model!$C$25</f>
+        <f>D$5*(1-$A6)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
       <c r="E6" s="51">
-        <f>E$5-Model!$C$19-$A6*Model!$C$24*Model!$C$25</f>
+        <f>E$5*(1-$A6)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
       <c r="F6" s="51">
-        <f>F$5-Model!$C$19-$A6*Model!$C$24*Model!$C$25</f>
+        <f>F$5*(1-$A6)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
       <c r="G6" s="51">
-        <f>G$5-Model!$C$19-$A6*Model!$C$24*Model!$C$25</f>
+        <f>G$5*(1-$A6)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
       <c r="H6" s="51">
-        <f>H$5-Model!$C$19-$A6*Model!$C$24*Model!$C$25</f>
+        <f>H$5*(1-$A6)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
       <c r="I6" s="51">
-        <f>I$5-Model!$C$19-$A6*Model!$C$24*Model!$C$25</f>
+        <f>I$5*(1-$A6)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="20" t="n">
-        <v>10</v>
+      <c r="A7" s="16" t="n">
+        <v>0.4</v>
       </c>
       <c r="B7" s="51">
-        <f>B$5-Model!$C$19-$A7*Model!$C$24*Model!$C$25</f>
+        <f>B$5*(1-$A7)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
       <c r="C7" s="51">
-        <f>C$5-Model!$C$19-$A7*Model!$C$24*Model!$C$25</f>
+        <f>C$5*(1-$A7)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
       <c r="D7" s="51">
-        <f>D$5-Model!$C$19-$A7*Model!$C$24*Model!$C$25</f>
+        <f>D$5*(1-$A7)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
       <c r="E7" s="51">
-        <f>E$5-Model!$C$19-$A7*Model!$C$24*Model!$C$25</f>
+        <f>E$5*(1-$A7)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
       <c r="F7" s="51">
-        <f>F$5-Model!$C$19-$A7*Model!$C$24*Model!$C$25</f>
+        <f>F$5*(1-$A7)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
       <c r="G7" s="51">
-        <f>G$5-Model!$C$19-$A7*Model!$C$24*Model!$C$25</f>
+        <f>G$5*(1-$A7)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
       <c r="H7" s="51">
-        <f>H$5-Model!$C$19-$A7*Model!$C$24*Model!$C$25</f>
+        <f>H$5*(1-$A7)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
       <c r="I7" s="51">
-        <f>I$5-Model!$C$19-$A7*Model!$C$24*Model!$C$25</f>
+        <f>I$5*(1-$A7)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="n">
-        <v>15</v>
+      <c r="A8" s="21" t="n">
+        <v>0.5</v>
       </c>
       <c r="B8" s="51">
-        <f>B$5-Model!$C$19-$A8*Model!$C$24*Model!$C$25</f>
+        <f>B$5*(1-$A8)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
       <c r="C8" s="51">
-        <f>C$5-Model!$C$19-$A8*Model!$C$24*Model!$C$25</f>
+        <f>C$5*(1-$A8)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
       <c r="D8" s="51">
-        <f>D$5-Model!$C$19-$A8*Model!$C$24*Model!$C$25</f>
+        <f>D$5*(1-$A8)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
       <c r="E8" s="51">
-        <f>E$5-Model!$C$19-$A8*Model!$C$24*Model!$C$25</f>
+        <f>E$5*(1-$A8)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
       <c r="F8" s="51">
-        <f>F$5-Model!$C$19-$A8*Model!$C$24*Model!$C$25</f>
+        <f>F$5*(1-$A8)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
       <c r="G8" s="51">
-        <f>G$5-Model!$C$19-$A8*Model!$C$24*Model!$C$25</f>
+        <f>G$5*(1-$A8)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
       <c r="H8" s="51">
-        <f>H$5-Model!$C$19-$A8*Model!$C$24*Model!$C$25</f>
+        <f>H$5*(1-$A8)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
       <c r="I8" s="51">
-        <f>I$5-Model!$C$19-$A8*Model!$C$24*Model!$C$25</f>
+        <f>I$5*(1-$A8)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="20" t="n">
-        <v>20</v>
+      <c r="A9" s="16" t="n">
+        <v>0.55</v>
       </c>
       <c r="B9" s="51">
-        <f>B$5-Model!$C$19-$A9*Model!$C$24*Model!$C$25</f>
+        <f>B$5*(1-$A9)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
       <c r="C9" s="51">
-        <f>C$5-Model!$C$19-$A9*Model!$C$24*Model!$C$25</f>
+        <f>C$5*(1-$A9)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
       <c r="D9" s="51">
-        <f>D$5-Model!$C$19-$A9*Model!$C$24*Model!$C$25</f>
+        <f>D$5*(1-$A9)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
       <c r="E9" s="51">
-        <f>E$5-Model!$C$19-$A9*Model!$C$24*Model!$C$25</f>
+        <f>E$5*(1-$A9)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
       <c r="F9" s="51">
-        <f>F$5-Model!$C$19-$A9*Model!$C$24*Model!$C$25</f>
+        <f>F$5*(1-$A9)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
       <c r="G9" s="51">
-        <f>G$5-Model!$C$19-$A9*Model!$C$24*Model!$C$25</f>
+        <f>G$5*(1-$A9)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
       <c r="H9" s="51">
-        <f>H$5-Model!$C$19-$A9*Model!$C$24*Model!$C$25</f>
+        <f>H$5*(1-$A9)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
       <c r="I9" s="51">
-        <f>I$5-Model!$C$19-$A9*Model!$C$24*Model!$C$25</f>
+        <f>I$5*(1-$A9)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="n">
-        <v>25</v>
+      <c r="A10" s="21" t="n">
+        <v>0.6</v>
       </c>
       <c r="B10" s="51">
-        <f>B$5-Model!$C$19-$A10*Model!$C$24*Model!$C$25</f>
+        <f>B$5*(1-$A10)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
       <c r="C10" s="51">
-        <f>C$5-Model!$C$19-$A10*Model!$C$24*Model!$C$25</f>
+        <f>C$5*(1-$A10)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
       <c r="D10" s="51">
-        <f>D$5-Model!$C$19-$A10*Model!$C$24*Model!$C$25</f>
+        <f>D$5*(1-$A10)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
       <c r="E10" s="51">
-        <f>E$5-Model!$C$19-$A10*Model!$C$24*Model!$C$25</f>
+        <f>E$5*(1-$A10)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
       <c r="F10" s="51">
-        <f>F$5-Model!$C$19-$A10*Model!$C$24*Model!$C$25</f>
+        <f>F$5*(1-$A10)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
       <c r="G10" s="51">
-        <f>G$5-Model!$C$19-$A10*Model!$C$24*Model!$C$25</f>
+        <f>G$5*(1-$A10)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
       <c r="H10" s="51">
-        <f>H$5-Model!$C$19-$A10*Model!$C$24*Model!$C$25</f>
+        <f>H$5*(1-$A10)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
       <c r="I10" s="51">
-        <f>I$5-Model!$C$19-$A10*Model!$C$24*Model!$C$25</f>
+        <f>I$5*(1-$A10)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="20" t="n">
-        <v>30</v>
+      <c r="A11" s="16" t="n">
+        <v>0.7</v>
       </c>
       <c r="B11" s="51">
-        <f>B$5-Model!$C$19-$A11*Model!$C$24*Model!$C$25</f>
+        <f>B$5*(1-$A11)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
       <c r="C11" s="51">
-        <f>C$5-Model!$C$19-$A11*Model!$C$24*Model!$C$25</f>
+        <f>C$5*(1-$A11)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
       <c r="D11" s="51">
-        <f>D$5-Model!$C$19-$A11*Model!$C$24*Model!$C$25</f>
+        <f>D$5*(1-$A11)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
       <c r="E11" s="51">
-        <f>E$5-Model!$C$19-$A11*Model!$C$24*Model!$C$25</f>
+        <f>E$5*(1-$A11)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
       <c r="F11" s="51">
-        <f>F$5-Model!$C$19-$A11*Model!$C$24*Model!$C$25</f>
+        <f>F$5*(1-$A11)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
       <c r="G11" s="51">
-        <f>G$5-Model!$C$19-$A11*Model!$C$24*Model!$C$25</f>
+        <f>G$5*(1-$A11)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
       <c r="H11" s="51">
-        <f>H$5-Model!$C$19-$A11*Model!$C$24*Model!$C$25</f>
+        <f>H$5*(1-$A11)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
       <c r="I11" s="51">
-        <f>I$5-Model!$C$19-$A11*Model!$C$24*Model!$C$25</f>
+        <f>I$5*(1-$A11)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="n">
-        <v>40</v>
+      <c r="A12" s="16" t="n">
+        <v>0.8</v>
       </c>
       <c r="B12" s="51">
-        <f>B$5-Model!$C$19-$A12*Model!$C$24*Model!$C$25</f>
+        <f>B$5*(1-$A12)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
       <c r="C12" s="51">
-        <f>C$5-Model!$C$19-$A12*Model!$C$24*Model!$C$25</f>
+        <f>C$5*(1-$A12)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
       <c r="D12" s="51">
-        <f>D$5-Model!$C$19-$A12*Model!$C$24*Model!$C$25</f>
+        <f>D$5*(1-$A12)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
       <c r="E12" s="51">
-        <f>E$5-Model!$C$19-$A12*Model!$C$24*Model!$C$25</f>
+        <f>E$5*(1-$A12)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
       <c r="F12" s="51">
-        <f>F$5-Model!$C$19-$A12*Model!$C$24*Model!$C$25</f>
+        <f>F$5*(1-$A12)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
       <c r="G12" s="51">
-        <f>G$5-Model!$C$19-$A12*Model!$C$24*Model!$C$25</f>
+        <f>G$5*(1-$A12)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
       <c r="H12" s="51">
-        <f>H$5-Model!$C$19-$A12*Model!$C$24*Model!$C$25</f>
+        <f>H$5*(1-$A12)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
       <c r="I12" s="51">
-        <f>I$5-Model!$C$19-$A12*Model!$C$24*Model!$C$25</f>
+        <f>I$5*(1-$A12)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="20" t="n">
-        <v>60</v>
+      <c r="A13" s="16" t="n">
+        <v>0.9</v>
       </c>
       <c r="B13" s="51">
-        <f>B$5-Model!$C$19-$A13*Model!$C$24*Model!$C$25</f>
+        <f>B$5*(1-$A13)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
       <c r="C13" s="51">
-        <f>C$5-Model!$C$19-$A13*Model!$C$24*Model!$C$25</f>
+        <f>C$5*(1-$A13)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
       <c r="D13" s="51">
-        <f>D$5-Model!$C$19-$A13*Model!$C$24*Model!$C$25</f>
+        <f>D$5*(1-$A13)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
       <c r="E13" s="51">
-        <f>E$5-Model!$C$19-$A13*Model!$C$24*Model!$C$25</f>
+        <f>E$5*(1-$A13)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
       <c r="F13" s="51">
-        <f>F$5-Model!$C$19-$A13*Model!$C$24*Model!$C$25</f>
+        <f>F$5*(1-$A13)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
       <c r="G13" s="51">
-        <f>G$5-Model!$C$19-$A13*Model!$C$24*Model!$C$25</f>
+        <f>G$5*(1-$A13)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
       <c r="H13" s="51">
-        <f>H$5-Model!$C$19-$A13*Model!$C$24*Model!$C$25</f>
+        <f>H$5*(1-$A13)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
       <c r="I13" s="51">
-        <f>I$5-Model!$C$19-$A13*Model!$C$24*Model!$C$25</f>
+        <f>I$5*(1-$A13)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="52" t="n">
-        <v>95</v>
+      <c r="A14" s="16" t="n">
+        <v>1</v>
       </c>
       <c r="B14" s="51">
-        <f>B$5-Model!$C$19-$A14*Model!$C$24*Model!$C$25</f>
+        <f>B$5*(1-$A14)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
       <c r="C14" s="51">
-        <f>C$5-Model!$C$19-$A14*Model!$C$24*Model!$C$25</f>
+        <f>C$5*(1-$A14)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
       <c r="D14" s="51">
-        <f>D$5-Model!$C$19-$A14*Model!$C$24*Model!$C$25</f>
+        <f>D$5*(1-$A14)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
       <c r="E14" s="51">
-        <f>E$5-Model!$C$19-$A14*Model!$C$24*Model!$C$25</f>
+        <f>E$5*(1-$A14)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
       <c r="F14" s="51">
-        <f>F$5-Model!$C$19-$A14*Model!$C$24*Model!$C$25</f>
+        <f>F$5*(1-$A14)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
       <c r="G14" s="51">
-        <f>G$5-Model!$C$19-$A14*Model!$C$24*Model!$C$25</f>
+        <f>G$5*(1-$A14)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
       <c r="H14" s="51">
-        <f>H$5-Model!$C$19-$A14*Model!$C$24*Model!$C$25</f>
+        <f>H$5*(1-$A14)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
       <c r="I14" s="51">
-        <f>I$5-Model!$C$19-$A14*Model!$C$24*Model!$C$25</f>
+        <f>I$5*(1-$A14)+Model!$C$36-Model!$C$32</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="24" t="inlineStr">
         <is>
-          <t>₹95 is the original design. Every negative cell on that row is a loss per user per month.</t>
+          <t>Shipped shares (50% and 60%) are highlighted. Every negative cell is a loss per user per month.</t>
         </is>
       </c>
     </row>
